--- a/AAII_Financials/Quarterly/BBBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BBBY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
   <si>
     <t>BBBY</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,149 +656,161 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>273400</v>
+      </c>
+      <c r="E8" s="3">
         <v>257200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>282300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>231700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>303200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>311400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>398100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>382300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>384500</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>206200</v>
+      </c>
+      <c r="E9" s="3">
         <v>192000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>215300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>173600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>233500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>245500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>317900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>307900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>310600</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>67300</v>
+      </c>
+      <c r="E10" s="3">
         <v>65200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>67000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>58100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>69700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>66000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>80200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>74400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>73900</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -810,37 +822,41 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E12" s="3">
         <v>20600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>23200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>26700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>30000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>27700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>27300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>29600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -868,66 +884,75 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-7600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-3200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>12900</v>
       </c>
-      <c r="G14" s="3">
-        <v>-15300</v>
-      </c>
       <c r="H14" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="I14" s="3">
         <v>12500</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>8700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-15800</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>900</v>
+      </c>
+      <c r="E15" s="3">
         <v>1200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -936,66 +961,73 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>287100</v>
+      </c>
+      <c r="E17" s="3">
         <v>269600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>300100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>255300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>346000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>355000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>445100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>439800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>449000</v>
       </c>
     </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-12500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-17900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-23500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-42900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-43600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-47000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-57500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-64600</v>
       </c>
     </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1007,71 +1039,78 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E20" s="3">
         <v>600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>4100</v>
       </c>
-      <c r="G20" s="3">
-        <v>53800</v>
-      </c>
       <c r="H20" s="3">
+        <v>53900</v>
+      </c>
+      <c r="I20" s="3">
         <v>6400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>10100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>49000</v>
       </c>
     </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-31100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-11800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-21800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-26200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-95400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-47900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-42400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-65600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-110800</v>
       </c>
     </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>10</v>
+      <c r="D22" s="3">
+        <v>1200</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>10</v>
@@ -1082,8 +1121,8 @@
       <c r="G22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>10</v>
+      <c r="H22" s="3">
+        <v>2200</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>10</v>
@@ -1094,66 +1133,75 @@
       <c r="K22" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-20800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-19000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-39700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-81200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-60800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-42500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-73600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-94600</v>
       </c>
     </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>66400</v>
       </c>
     </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1181,66 +1229,75 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-19300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-39900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-81300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-61000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-42600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-73900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-161000</v>
       </c>
     </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-19300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-39900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-81300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-61000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-42600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-73900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-161000</v>
       </c>
     </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1268,8 +1325,11 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1297,8 +1357,11 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1326,8 +1389,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1355,66 +1421,75 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-4100</v>
       </c>
-      <c r="G32" s="3">
-        <v>-53800</v>
-      </c>
       <c r="H32" s="3">
+        <v>-53900</v>
+      </c>
+      <c r="I32" s="3">
         <v>-6400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-10100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-49000</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-19300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-39900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-81300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-61000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-42600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-73900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-161000</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1442,71 +1517,80 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-19300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-39900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-81300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-61000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-42600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-73900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-161000</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1518,8 +1602,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1531,37 +1616,41 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>175300</v>
+      </c>
+      <c r="E41" s="3">
         <v>167400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>120600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>114600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>159200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>140400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>186200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>256300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>302600</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1589,71 +1678,80 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E43" s="3">
         <v>17300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>23300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>18100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>15800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>15000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>18700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>23100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>19400</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E44" s="3">
         <v>7200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>8400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>24600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>11500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>11100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>12100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>12900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>13000</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>10</v>
+      <c r="D45" s="3">
+        <v>1500</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>10</v>
@@ -1661,11 +1759,11 @@
       <c r="F45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H45" s="3">
         <v>1900</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>10</v>
@@ -1673,127 +1771,142 @@
       <c r="J45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L45" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>240100</v>
+      </c>
+      <c r="E46" s="3">
         <v>231800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>195900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>196500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>227500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>183100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>232200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>305400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>350100</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>109000</v>
+      </c>
+      <c r="E47" s="3">
         <v>104400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>94400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>95900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>104000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>112500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>129700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>137400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>166400</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E48" s="3">
         <v>20200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>22200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>25600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>30400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>29200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>30800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>30100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>51300</v>
+      </c>
+      <c r="E49" s="3">
         <v>51500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>38700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>38900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>36400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>36700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>37100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>37200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>31400</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1821,8 +1934,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1850,37 +1966,43 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E52" s="3">
         <v>6500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3700</v>
-      </c>
-      <c r="H52" s="3">
-        <v>67000</v>
       </c>
       <c r="I52" s="3">
         <v>67000</v>
       </c>
       <c r="J52" s="3">
+        <v>67000</v>
+      </c>
+      <c r="K52" s="3">
         <v>67100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>56900</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1908,37 +2030,43 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>425500</v>
+      </c>
+      <c r="E54" s="3">
         <v>414400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>358100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>363700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>402000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>428300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>496800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>577300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>635800</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1950,8 +2078,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1963,182 +2092,201 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>90000</v>
+      </c>
+      <c r="E57" s="3">
         <v>94200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>111400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>78000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>81900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>88000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>91200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>116300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>106100</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E58" s="3">
         <v>18900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>19300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>25700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>26200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>42200</v>
+      </c>
+      <c r="E59" s="3">
         <v>42900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>45900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>48500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>52600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>52000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>56900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>65200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>58200</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>192100</v>
+      </c>
+      <c r="E60" s="3">
         <v>197800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>215400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>206100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>224900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>189000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>203000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>245900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>232400</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E61" s="3">
         <v>5900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6500</v>
-      </c>
-      <c r="H61" s="3">
-        <v>34600</v>
       </c>
       <c r="I61" s="3">
         <v>34600</v>
       </c>
       <c r="J61" s="3">
+        <v>34600</v>
+      </c>
+      <c r="K61" s="3">
         <v>34800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>35200</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E62" s="3">
         <v>7800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>8800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2166,8 +2314,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2195,8 +2346,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2224,37 +2378,43 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>207500</v>
+      </c>
+      <c r="E66" s="3">
         <v>211400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>226900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>220400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>239200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>232100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>246400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>289500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>276700</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2266,8 +2426,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2295,8 +2456,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2324,8 +2488,11 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2353,8 +2520,11 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2382,37 +2552,43 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-842700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-804200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-799700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-780400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-740500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-659200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-598200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-555600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-481700</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2440,8 +2616,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2469,8 +2648,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2498,37 +2680,43 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>217600</v>
+      </c>
+      <c r="E76" s="3">
         <v>202600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>130900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>143400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>162700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>196200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>250400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>287700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>359100</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2556,71 +2744,80 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-19300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-39900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-81300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-61000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-42600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-73900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-161000</v>
       </c>
     </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2632,37 +2829,41 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E83" s="3">
         <v>2000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3100</v>
-      </c>
-      <c r="I83" s="3">
-        <v>2900</v>
       </c>
       <c r="J83" s="3">
         <v>2900</v>
       </c>
       <c r="K83" s="3">
+        <v>2900</v>
+      </c>
+      <c r="L83" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2690,8 +2891,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2719,8 +2923,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2748,8 +2955,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2777,8 +2987,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2806,37 +3019,43 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-15100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>15800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-50900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-21700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-42100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-75900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-34600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-27700</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2848,37 +3067,41 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2906,8 +3129,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2935,37 +3161,43 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-10200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>31500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>5800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2977,8 +3209,9 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3006,8 +3239,11 @@
       <c r="K96" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3035,8 +3271,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3064,8 +3303,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3093,37 +3335,43 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>33100</v>
+      </c>
+      <c r="E100" s="3">
         <v>72200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>19500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>34800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3151,33 +3399,39 @@
       <c r="K101" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E102" s="3">
         <v>46900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>6100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-44600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>44600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-44800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-70200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-46300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-22700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BBBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BBBY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
   <si>
     <t>BBBY</t>
   </si>
@@ -656,161 +656,174 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>247800</v>
+      </c>
+      <c r="E8" s="3">
         <v>273400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>257200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>282300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>231700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>303200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>311400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>398100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>382300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>384500</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>188600</v>
+      </c>
+      <c r="E9" s="3">
         <v>206200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>192000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>215300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>173600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>233500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>245500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>317900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>307900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>310600</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>59200</v>
+      </c>
+      <c r="E10" s="3">
         <v>67300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>65200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>67000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>58100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>69700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>66000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>80200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>74400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>73900</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -823,40 +836,44 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E12" s="3">
         <v>19700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>20600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>23200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>26700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>30000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>27700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>27300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>29600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -887,72 +904,81 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E14" s="3">
         <v>-9000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-7600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-3200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>12900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-15400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>12500</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>8700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-15800</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>500</v>
+      </c>
+      <c r="E15" s="3">
         <v>900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -962,72 +988,79 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>266000</v>
+      </c>
+      <c r="E17" s="3">
         <v>287100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>269600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>300100</v>
       </c>
-      <c r="G17" s="3">
-        <v>255300</v>
-      </c>
       <c r="H17" s="3">
+        <v>255000</v>
+      </c>
+      <c r="I17" s="3">
         <v>346000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>355000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>445100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>439800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>449000</v>
       </c>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-18200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-13600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-12500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-17900</v>
       </c>
-      <c r="G18" s="3">
-        <v>-23500</v>
-      </c>
       <c r="H18" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="I18" s="3">
         <v>-42900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-43600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-47000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-57500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-64600</v>
       </c>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1040,80 +1073,87 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E20" s="3">
         <v>18400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5200</v>
       </c>
-      <c r="G20" s="3">
-        <v>4100</v>
-      </c>
       <c r="H20" s="3">
+        <v>4400</v>
+      </c>
+      <c r="I20" s="3">
         <v>53900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>6400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>10100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>49000</v>
       </c>
     </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-31100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-11800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-21800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-26200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-95400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-47900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-42400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-65600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-110800</v>
       </c>
     </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="3">
         <v>1200</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>10</v>
@@ -1121,11 +1161,11 @@
       <c r="G22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I22" s="3">
         <v>2200</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>10</v>
@@ -1136,72 +1176,81 @@
       <c r="L22" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-20800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-19000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-39700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-81200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-60800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-42500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-73600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-94600</v>
       </c>
     </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>66400</v>
       </c>
     </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1232,72 +1281,81 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-20900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-4500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-19300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-39900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-81300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-61000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-42600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-73900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-161000</v>
       </c>
     </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-20900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-4500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-19300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-39900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-81300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-61000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-42600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-73900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-161000</v>
       </c>
     </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1328,8 +1386,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1360,8 +1421,11 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1392,8 +1456,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1424,72 +1491,81 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-18400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5200</v>
       </c>
-      <c r="G32" s="3">
-        <v>-4100</v>
-      </c>
       <c r="H32" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="I32" s="3">
         <v>-53900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-6400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-10100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-49000</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-20900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-4500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-19300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-39900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-81300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-61000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-42600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-73900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-161000</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1520,77 +1596,86 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-20900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-4500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-19300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-39900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-81300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-61000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-42600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-73900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-161000</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1603,8 +1688,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1617,40 +1703,44 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>135800</v>
+      </c>
+      <c r="E41" s="3">
         <v>175300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>167400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>120600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>114600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>159200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>140400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>186200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>256300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>302600</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1681,80 +1771,89 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E43" s="3">
         <v>20800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>17300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>23300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>18100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>15800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>15000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>18700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>23100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>19400</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>500</v>
+      </c>
+      <c r="E44" s="3">
         <v>5200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>7200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>8400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>24600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>11500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>11100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>12100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>12900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>13000</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="3">
         <v>1500</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>10</v>
@@ -1762,11 +1861,11 @@
       <c r="G45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I45" s="3">
         <v>1900</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>10</v>
@@ -1774,139 +1873,154 @@
       <c r="K45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M45" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>196700</v>
+      </c>
+      <c r="E46" s="3">
         <v>240100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>231800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>195900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>196500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>227500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>183100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>232200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>305400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>350100</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>133200</v>
+      </c>
+      <c r="E47" s="3">
         <v>109000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>104400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>94400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>95900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>104000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>112500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>129700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>137400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>166400</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E48" s="3">
         <v>18900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>20200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>22200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>25600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>30400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>29200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>30800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>30100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>51200</v>
+      </c>
+      <c r="E49" s="3">
         <v>51300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>51500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>38700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>38900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>36400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>36700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>37100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>37200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>31400</v>
       </c>
     </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1937,8 +2051,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1969,40 +2086,46 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E52" s="3">
         <v>6200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>6800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3700</v>
-      </c>
-      <c r="I52" s="3">
-        <v>67000</v>
       </c>
       <c r="J52" s="3">
         <v>67000</v>
       </c>
       <c r="K52" s="3">
+        <v>67000</v>
+      </c>
+      <c r="L52" s="3">
         <v>67100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>56900</v>
       </c>
     </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2033,40 +2156,46 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>404500</v>
+      </c>
+      <c r="E54" s="3">
         <v>425500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>414400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>358100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>363700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>402000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>428300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>496800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>577300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>635800</v>
       </c>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2079,8 +2208,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2093,40 +2223,44 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>91500</v>
+      </c>
+      <c r="E57" s="3">
         <v>90000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>94200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>111400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>78000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>81900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>88000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>91200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>116300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>106100</v>
       </c>
     </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2134,159 +2268,174 @@
         <v>16400</v>
       </c>
       <c r="E58" s="3">
+        <v>16400</v>
+      </c>
+      <c r="F58" s="3">
         <v>18900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>19300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>25700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>26200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>40700</v>
+      </c>
+      <c r="E59" s="3">
         <v>42200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>42900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>45900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>48500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>52600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>52000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>56900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>65200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>58200</v>
       </c>
     </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>190100</v>
+      </c>
+      <c r="E60" s="3">
         <v>192100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>197800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>215400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>206100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>224900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>189000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>203000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>245900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>232400</v>
       </c>
     </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E61" s="3">
         <v>5600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6500</v>
-      </c>
-      <c r="I61" s="3">
-        <v>34600</v>
       </c>
       <c r="J61" s="3">
         <v>34600</v>
       </c>
       <c r="K61" s="3">
+        <v>34600</v>
+      </c>
+      <c r="L61" s="3">
         <v>34800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>35200</v>
       </c>
     </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E62" s="3">
         <v>7300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>7800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>8700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2317,8 +2466,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2349,8 +2501,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2381,40 +2536,46 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>202000</v>
+      </c>
+      <c r="E66" s="3">
         <v>207500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>211400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>226900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>220400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>239200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>232100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>246400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>289500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>276700</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2427,8 +2588,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2459,8 +2621,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2491,8 +2656,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2523,8 +2691,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2555,40 +2726,46 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-859100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-842700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-804200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-799700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-780400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-740500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-659200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-598200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-555600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-481700</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2619,8 +2796,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2651,8 +2831,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2683,40 +2866,46 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>202100</v>
+      </c>
+      <c r="E76" s="3">
         <v>217600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>202600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>130900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>143400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>162700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>196200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>250400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>287700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>359100</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2747,77 +2936,86 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-20900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-4500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-19300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-39900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-81300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-61000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-42600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-73900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-161000</v>
       </c>
     </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2830,40 +3028,44 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E83" s="3">
         <v>1300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3100</v>
-      </c>
-      <c r="J83" s="3">
-        <v>2900</v>
       </c>
       <c r="K83" s="3">
         <v>2900</v>
       </c>
       <c r="L83" s="3">
+        <v>2900</v>
+      </c>
+      <c r="M83" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2894,8 +3096,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2926,8 +3131,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2958,8 +3166,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2990,8 +3201,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3022,40 +3236,46 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-6500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-15100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>15800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-50900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-21700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-42100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-75900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-34600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-27700</v>
       </c>
     </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3068,40 +3288,44 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3132,8 +3356,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3164,40 +3391,46 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-27300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-18800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-10200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-13100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>31500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>5800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3210,8 +3443,9 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3242,8 +3476,11 @@
       <c r="L96" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3274,8 +3511,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3306,8 +3546,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3338,40 +3581,46 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E100" s="3">
         <v>33100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>72200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>19500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>34800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3402,36 +3651,42 @@
       <c r="L101" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-39700</v>
+      </c>
+      <c r="E102" s="3">
         <v>7800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>46900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>6100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-44600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>44600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-44800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-70200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-46300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-22700</v>
       </c>
     </row>
